--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_329_R33.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_329_R33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1807</v>
+        <v>5.5704</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6587</v>
+        <v>2.082</v>
       </c>
       <c r="F2" t="n">
-        <v>3.522</v>
+        <v>3.4884</v>
       </c>
       <c r="G2" t="n">
         <v>2.0893</v>
@@ -610,13 +610,13 @@
         <v>3.4793</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6996</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0998</v>
+        <v>0.5232</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4002</v>
+        <v>-0.4338</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9282</v>
+        <v>4.2901</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7133</v>
+        <v>2.3777</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2149</v>
+        <v>1.9124</v>
       </c>
       <c r="G3" t="n">
         <v>4.4222</v>
@@ -688,13 +688,13 @@
         <v>3.4793</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9553</v>
+        <v>-1.5933</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1202</v>
+        <v>-0.4558</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8351</v>
+        <v>-1.1376</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3943</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9341</v>
+        <v>3.1705</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1195</v>
+        <v>0.7808</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0536</v>
+        <v>2.3896</v>
       </c>
       <c r="G4" t="n">
         <v>1.0374</v>
@@ -766,13 +766,13 @@
         <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.1034</v>
+        <v>-0.867</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0455</v>
+        <v>-0.1452</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0578</v>
+        <v>-0.7218</v>
       </c>
       <c r="V4" t="n">
         <v>1.6083</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SIRVYDIS</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3357</v>
+        <v>1.7264</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7324000000000001</v>
+        <v>-0.7085</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6032999999999999</v>
+        <v>2.4349</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4731</v>
+        <v>-1.8305</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1585</v>
+        <v>-3.731</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3145</v>
+        <v>1.9005</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0336</v>
+        <v>-1.2974</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0336</v>
+        <v>-2.9402</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.6428</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4395</v>
+        <v>-0.533</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1249</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3145</v>
+        <v>0.2578</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>3.4793</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>3.7112</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1373</v>
+        <v>-0.9946</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3734</v>
+        <v>-0.2513</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7639</v>
+        <v>-0.7433</v>
       </c>
       <c r="V5" t="n">
         <v>1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>D. SIRVYDIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8054</v>
+        <v>1.4873</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2701</v>
+        <v>0.8504</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0755</v>
+        <v>0.6369</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.4731</v>
       </c>
       <c r="H6" t="n">
-        <v>0.604</v>
+        <v>0.1585</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5957</v>
+        <v>0.3145</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3739</v>
+        <v>0.0336</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2185</v>
+        <v>0.0336</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5924</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3823</v>
+        <v>0.4395</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3856</v>
+        <v>0.1249</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0033</v>
+        <v>0.3145</v>
       </c>
       <c r="P6" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9142</v>
+        <v>-0.9858</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8962</v>
+        <v>-0.2555</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.018</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3048</v>
+        <v>1.1838</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7268</v>
+        <v>-0.7236</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0316</v>
+        <v>1.9075</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8305</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.731</v>
+        <v>0.604</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9005</v>
+        <v>-0.5957</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2974</v>
+        <v>-0.3739</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.9402</v>
+        <v>0.2185</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6428</v>
+        <v>-0.5924</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.533</v>
+        <v>0.3823</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7907999999999999</v>
+        <v>0.3856</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2578</v>
+        <v>-0.0033</v>
       </c>
       <c r="P7" t="n">
-        <v>3.4793</v>
+        <v>2.7834</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.7112</v>
+        <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.4162</v>
+        <v>-0.5357</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2696</v>
+        <v>-0.3497</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1466</v>
+        <v>-0.186</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1431</v>
+        <v>-0.7534</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.1964</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.9498</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5047</v>
+        <v>-0.4448</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1199</v>
+        <v>-0.3913</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3848</v>
+        <v>-0.0535</v>
       </c>
       <c r="J8" t="n">
-        <v>0.104</v>
+        <v>0.3025</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0672</v>
+        <v>0.3025</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6087</v>
+        <v>-0.7473</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1871</v>
+        <v>-0.6938</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4216</v>
+        <v>-0.0535</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5756</v>
+        <v>-0.3086</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9856</v>
+        <v>-0.1061</v>
       </c>
       <c r="U8" t="n">
-        <v>0.59</v>
+        <v>-0.2025</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.9298</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1215</v>
+        <v>-1.1232</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4173</v>
+        <v>0.1934</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7679</v>
+        <v>-1.0498</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4069</v>
+        <v>-0.9962</v>
       </c>
       <c r="I9" t="n">
-        <v>0.639</v>
+        <v>-0.0535</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0382</v>
+        <v>-0.4669</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9978</v>
+        <v>-0.4166</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0403</v>
+        <v>-0.0502</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7298</v>
+        <v>-0.5829</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4091</v>
+        <v>-0.5796</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6793</v>
+        <v>-0.0033</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.6237</v>
+        <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>2.157</v>
+        <v>0.3519</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3986</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2416</v>
+        <v>-0.3835</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9386</v>
+        <v>-1.3896</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0784</v>
+        <v>-0.3676</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.017</v>
+        <v>-1.022</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4448</v>
+        <v>-1.5047</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3913</v>
+        <v>-1.1199</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0535</v>
+        <v>-0.3848</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3025</v>
+        <v>0.104</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3025</v>
+        <v>0.0672</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.0368</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7473</v>
+        <v>-1.6087</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6938</v>
+        <v>-1.1871</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0535</v>
+        <v>-0.4216</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4938</v>
+        <v>1.0429</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.224</v>
+        <v>0.6882</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2697</v>
+        <v>0.3547</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4689</v>
+        <v>-1.6675</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.595</v>
+        <v>-1.183</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1262</v>
+        <v>-0.4845</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0498</v>
+        <v>-1.7679</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9962</v>
+        <v>-2.4069</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0535</v>
+        <v>0.639</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4669</v>
+        <v>-1.0382</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4166</v>
+        <v>-0.9978</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0502</v>
+        <v>-0.0403</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5829</v>
+        <v>-0.7298</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5796</v>
+        <v>-1.4091</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0033</v>
+        <v>0.6793</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3917</v>
+        <v>-1.6237</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1871</v>
+        <v>1.0282</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2636</v>
+        <v>1.337</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4507</v>
+        <v>-0.3088</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7354</v>
+        <v>-2.4323</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8865</v>
+        <v>-1.6506</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.849</v>
+        <v>-0.7817</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1411</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5764</v>
+        <v>-0.2732</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1494</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.427</v>
+        <v>-0.3598</v>
       </c>
       <c r="V12" t="n">
         <v>0.1418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2242</v>
+        <v>-3.1563</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3189</v>
+        <v>-2.083</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9053</v>
+        <v>-1.0733</v>
       </c>
       <c r="G13" t="n">
         <v>-2.491</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6585</v>
+        <v>0.7264</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3383</v>
+        <v>0.5742</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3203</v>
+        <v>0.1522</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.726100000000001</v>
+        <v>7.099600000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.925600000000001</v>
+        <v>-1.5522</v>
       </c>
       <c r="F14" t="n">
-        <v>8.651700000000002</v>
+        <v>8.6518</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.199399999999999</v>
+        <v>-2.199400000000001</v>
       </c>
       <c r="H14" t="n">
         <v>-2.466899999999999</v>
@@ -1519,10 +1519,10 @@
         <v>0.2674000000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2725</v>
+        <v>2.272500000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>3.545000000000001</v>
+        <v>3.545</v>
       </c>
       <c r="L14" t="n">
         <v>-1.2724</v>
@@ -1537,7 +1537,7 @@
         <v>1.54</v>
       </c>
       <c r="P14" t="n">
-        <v>8.1182</v>
+        <v>8.118199999999998</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.5979</v>
@@ -1546,13 +1546,13 @@
         <v>19.7161</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.693000000000001</v>
+        <v>-2.3194</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0076</v>
+        <v>2.3809</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.700300000000001</v>
+        <v>-4.7005</v>
       </c>
       <c r="V14" t="n">
         <v>3.5002</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9631</v>
+        <v>2.8019</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6971</v>
+        <v>2.0378</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2661</v>
+        <v>0.764</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5576</v>
+        <v>2.179</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6215</v>
+        <v>1.5533</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.064</v>
+        <v>0.6257</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.336</v>
+        <v>1.5856</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0895</v>
+        <v>0.6421</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4255</v>
+        <v>0.9435</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8935999999999999</v>
+        <v>0.5935</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5321</v>
+        <v>0.9113</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3615</v>
+        <v>-0.3178</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3154</v>
+        <v>-0.1632</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1928</v>
+        <v>0.4523</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1226</v>
+        <v>-0.6155</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1418</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8526</v>
+        <v>2.0743</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1558</v>
+        <v>2.746</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6968</v>
+        <v>-0.6718</v>
       </c>
       <c r="G16" t="n">
-        <v>2.179</v>
+        <v>0.1683</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5533</v>
+        <v>-0.4775</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6257</v>
+        <v>0.6458</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5856</v>
+        <v>1.2054</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6421</v>
+        <v>0.9747</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9435</v>
+        <v>0.2308</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5935</v>
+        <v>-1.0372</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9113</v>
+        <v>-1.4522</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3178</v>
+        <v>0.415</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1125</v>
+        <v>0.3725</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5702</v>
+        <v>0.3266</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6827</v>
+        <v>0.0459</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1418</v>
+        <v>0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6196</v>
+        <v>1.8242</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3922</v>
+        <v>-0.0722</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7726</v>
+        <v>1.8964</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1683</v>
+        <v>0.5576</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4775</v>
+        <v>1.6215</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6458</v>
+        <v>-1.064</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2054</v>
+        <v>-0.336</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9747</v>
+        <v>1.0895</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2308</v>
+        <v>-1.4255</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0372</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4522</v>
+        <v>0.5321</v>
       </c>
       <c r="O17" t="n">
-        <v>0.415</v>
+        <v>0.3615</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.08210000000000001</v>
+        <v>1.1764</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0272</v>
+        <v>1.4235</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0549</v>
+        <v>-0.2471</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1418</v>
+        <v>-0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2248</v>
+        <v>0.9861</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7766</v>
+        <v>-0.1815</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5518</v>
+        <v>1.1676</v>
       </c>
       <c r="G18" t="n">
-        <v>4.455</v>
+        <v>0.0289</v>
       </c>
       <c r="H18" t="n">
-        <v>1.892</v>
+        <v>-0.443</v>
       </c>
       <c r="I18" t="n">
-        <v>2.563</v>
+        <v>0.4718</v>
       </c>
       <c r="J18" t="n">
-        <v>4.337</v>
+        <v>-0.7359</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6637</v>
+        <v>-0.7359</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6733</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.118</v>
+        <v>0.7648</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2283</v>
+        <v>0.293</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1103</v>
+        <v>0.4718</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.7834</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1615</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9189</v>
+        <v>0.5544</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7573</v>
+        <v>0.4028</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.9204</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6533</v>
+        <v>2.0689</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5037</v>
+        <v>-1.1485</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0289</v>
+        <v>4.455</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.443</v>
+        <v>1.892</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4718</v>
+        <v>2.563</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7359</v>
+        <v>4.337</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7359</v>
+        <v>1.6637</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.6733</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7648</v>
+        <v>0.118</v>
       </c>
       <c r="N19" t="n">
-        <v>0.293</v>
+        <v>0.2283</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4718</v>
+        <v>-0.1103</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8215</v>
+        <v>0.8571</v>
       </c>
       <c r="T19" t="n">
-        <v>0.08260000000000001</v>
+        <v>1.2111</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7389</v>
+        <v>-0.3541</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. MIKE</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6096</v>
+        <v>-0.2864</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3654</v>
+        <v>-1.8769</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2442</v>
+        <v>1.5905</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4467</v>
+        <v>-0.2205</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2268</v>
+        <v>2.0816</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7801</v>
+        <v>-2.3021</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5976</v>
+        <v>-0.7174</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1323</v>
+        <v>1.2134</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7298</v>
+        <v>-1.9308</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0443</v>
+        <v>0.4968</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0945</v>
+        <v>0.8681</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0502</v>
+        <v>-0.3713</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.253</v>
+        <v>-0.7617</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1968</v>
+        <v>0.0002</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4498</v>
+        <v>-0.762</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>I. MIKE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7857</v>
+        <v>-0.5767</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9023</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1167</v>
+        <v>0.0246</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2637</v>
+        <v>-0.4467</v>
       </c>
       <c r="H21" t="n">
-        <v>0.461</v>
+        <v>-2.2268</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1973</v>
+        <v>1.7801</v>
       </c>
       <c r="J21" t="n">
-        <v>0.303</v>
+        <v>0.5976</v>
       </c>
       <c r="K21" t="n">
-        <v>0.39</v>
+        <v>-1.1323</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0871</v>
+        <v>1.7298</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0393</v>
+        <v>-1.0443</v>
       </c>
       <c r="N21" t="n">
-        <v>0.07099999999999999</v>
+        <v>-1.0945</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1103</v>
+        <v>0.0502</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4841</v>
+        <v>-0.2201</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1142</v>
+        <v>-0.0391</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3699</v>
+        <v>-0.181</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1418</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0442</v>
+        <v>-1.0203</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4667</v>
+        <v>-1.6664</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4224</v>
+        <v>0.6462</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2205</v>
+        <v>0.2637</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0816</v>
+        <v>0.461</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3021</v>
+        <v>-0.1973</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7174</v>
+        <v>0.303</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2134</v>
+        <v>0.39</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9308</v>
+        <v>-0.0871</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4968</v>
+        <v>-0.0393</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8681</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3713</v>
+        <v>-0.1103</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6959</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5195</v>
+        <v>0.2495</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5895</v>
+        <v>0.3501</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.93</v>
+        <v>-0.1006</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4027</v>
+        <v>-1.5365</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2487</v>
+        <v>-1.0128</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.154</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2639</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1111</v>
+        <v>-0.0226</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2908</v>
+        <v>-0.0549</v>
       </c>
       <c r="U23" t="n">
-        <v>0.402</v>
+        <v>0.0323</v>
       </c>
       <c r="V23" t="n">
         <v>0.1418</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0646</v>
+        <v>-3.8801</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3016</v>
+        <v>-3.4195</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.763</v>
+        <v>-0.4606</v>
       </c>
       <c r="G24" t="n">
         <v>0.1067</v>
@@ -2326,13 +2326,13 @@
         <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6199</v>
+        <v>-0.4353</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1221</v>
+        <v>0.0042</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.742</v>
+        <v>-0.4395</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.3299</v>
+        <v>-8.033099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.7354</v>
+        <v>-6.6738</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5946</v>
+        <v>-1.3593</v>
       </c>
       <c r="G25" t="n">
         <v>-4.6287</v>
@@ -2404,13 +2404,13 @@
         <v>0.4639</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6137</v>
+        <v>0.6831</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5895</v>
+        <v>0.472</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0242</v>
+        <v>0.2111</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.726300000000001</v>
+        <v>-6.7262</v>
       </c>
       <c r="E26" t="n">
         <v>-8.651700000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>1.925500000000001</v>
+        <v>1.9254</v>
       </c>
       <c r="G26" t="n">
         <v>2.199399999999999</v>
@@ -2458,10 +2458,10 @@
         <v>4.471700000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>6.011799999999999</v>
+        <v>6.011800000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.540100000000001</v>
+        <v>-1.5401</v>
       </c>
       <c r="M26" t="n">
         <v>-2.2725</v>
@@ -2482,13 +2482,13 @@
         <v>11.5976</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6929</v>
+        <v>2.692899999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>4.7006</v>
+        <v>4.7004</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.0075</v>
+        <v>-2.0077</v>
       </c>
       <c r="V26" t="n">
         <v>-3.5002</v>
